--- a/output/pdf_financials_xlsx/AGC.xlsx
+++ b/output/pdf_financials_xlsx/AGC.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.281038</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.242141</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.281038</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.242141</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="37">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
